--- a/02_DIA_inicio_2026_analisis_assets/rbd_9600_escuela-nanihue_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9600_escuela-nanihue_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5ADFEA6-02B7-4EC4-BA2D-D5882210793D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7082A71F-1BCA-4E76-88D6-D9D9DFE82DBA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E258BA9-119B-4A10-B5E8-11FD83F1F172}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198B97ED-E003-4E6C-9611-D0147504E3BB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C00DB8B-494F-4181-9458-6156F8FEC8D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4555232E-2F3C-4E1D-8736-F3C9B5D94C23}"/>
 </file>